--- a/data/trans_dic/P1423-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,88</t>
+          <t>1,2; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,83</t>
+          <t>1,41; 4,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,68</t>
+          <t>1,35; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,7</t>
+          <t>2,92; 6,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,93</t>
+          <t>2,95; 8,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,23</t>
+          <t>2,45; 7,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,24</t>
+          <t>2,85; 7,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,94</t>
+          <t>5,9; 10,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,84</t>
+          <t>2,32; 4,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,45</t>
+          <t>2,33; 5,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,29</t>
+          <t>2,34; 5,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,62</t>
+          <t>4,85; 7,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,34</t>
+          <t>0,95; 4,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,73</t>
+          <t>1,7; 5,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,17</t>
+          <t>0,98; 4,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,18</t>
+          <t>3,9; 8,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,76</t>
+          <t>3,9; 9,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,77</t>
+          <t>3,57; 8,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,0</t>
+          <t>2,48; 6,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,57</t>
+          <t>7,69; 13,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,74</t>
+          <t>2,86; 5,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,21</t>
+          <t>2,8; 5,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,74</t>
+          <t>2,07; 4,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,72</t>
+          <t>6,04; 9,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,7</t>
+          <t>2,27; 5,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,15</t>
+          <t>4,74; 9,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,02</t>
+          <t>2,48; 5,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,42</t>
+          <t>1,72; 8,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 16,0</t>
+          <t>6,1; 16,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 19,19</t>
+          <t>10,68; 18,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 20,57</t>
+          <t>8,76; 20,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 17,53</t>
+          <t>9,75; 17,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,16</t>
+          <t>3,85; 7,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,28</t>
+          <t>7,0; 11,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,43</t>
+          <t>4,67; 8,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,89</t>
+          <t>2,85; 9,77</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,21</t>
+          <t>2,36; 4,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,34</t>
+          <t>3,41; 6,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,69</t>
+          <t>2,44; 4,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,54</t>
+          <t>4,6; 7,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,34</t>
+          <t>5,92; 10,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 13,29</t>
+          <t>8,82; 13,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,9</t>
+          <t>6,85; 10,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 12,19</t>
+          <t>5,25; 12,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,05</t>
+          <t>4,07; 5,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,51</t>
+          <t>6,04; 8,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 6,72</t>
+          <t>4,62; 6,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,86</t>
+          <t>5,15; 8,81</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,32</t>
+          <t>2,94; 7,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,13</t>
+          <t>1,96; 5,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,89</t>
+          <t>2,7; 5,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,37</t>
+          <t>5,45; 10,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,99</t>
+          <t>7,05; 11,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 17,57</t>
+          <t>12,49; 17,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 18,11</t>
+          <t>12,55; 17,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,57</t>
+          <t>11,34; 17,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,38</t>
+          <t>5,97; 9,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,11</t>
+          <t>8,7; 12,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,02</t>
+          <t>8,54; 11,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 14,12</t>
+          <t>9,91; 14,36</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,84</t>
+          <t>0,97; 5,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,2</t>
+          <t>0,33; 3,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 11,42</t>
+          <t>2,8; 11,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,93</t>
+          <t>5,61; 8,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,62</t>
+          <t>10,44; 14,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,36</t>
+          <t>9,59; 13,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,45; 14,81</t>
+          <t>10,53; 14,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,62</t>
+          <t>5,21; 7,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,59; 11,78</t>
+          <t>8,38; 11,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,04</t>
+          <t>7,79; 10,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,71</t>
+          <t>9,01; 12,95</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,76</t>
+          <t>2,51; 3,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,92</t>
+          <t>3,39; 4,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,95</t>
+          <t>2,65; 3,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,66</t>
+          <t>4,41; 6,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,4</t>
+          <t>6,64; 8,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,48</t>
+          <t>10,44; 12,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,11; 11,37</t>
+          <t>9,22; 11,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 12,49</t>
+          <t>9,27; 12,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,95</t>
+          <t>4,86; 5,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,52</t>
+          <t>7,22; 8,59</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,49</t>
+          <t>6,21; 7,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 9,41</t>
+          <t>7,4; 9,31</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5599; 18385</t>
+          <t>5678; 18791</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6215; 21105</t>
+          <t>6146; 20517</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5674; 20077</t>
+          <t>5795; 20168</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15079; 33846</t>
+          <t>14738; 35004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9330; 24308</t>
+          <t>9051; 24603</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8064; 25895</t>
+          <t>7708; 23787</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10280; 28613</t>
+          <t>9903; 27403</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25765; 44478</t>
+          <t>26419; 45402</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17490; 37748</t>
+          <t>18125; 38270</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16920; 40938</t>
+          <t>17542; 39465</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18345; 41094</t>
+          <t>18196; 40243</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46313; 72593</t>
+          <t>46205; 72919</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4018; 15930</t>
+          <t>3489; 15537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7029; 23998</t>
+          <t>7138; 24390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3989; 15722</t>
+          <t>3697; 15952</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18015; 37011</t>
+          <t>17633; 37579</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13988; 32571</t>
+          <t>14485; 33748</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11258; 29641</t>
+          <t>12067; 29878</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9235; 26070</t>
+          <t>9241; 25377</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29892; 51923</t>
+          <t>29412; 50280</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20430; 42424</t>
+          <t>21138; 41527</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21766; 46975</t>
+          <t>21192; 45324</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16101; 35532</t>
+          <t>15514; 35819</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51819; 81131</t>
+          <t>50447; 79993</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12657; 30917</t>
+          <t>12334; 29176</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30836; 57619</t>
+          <t>29839; 57032</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12647; 31417</t>
+          <t>12932; 31094</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10881; 56281</t>
+          <t>11519; 57600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10432; 26840</t>
+          <t>10236; 27352</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27194; 49921</t>
+          <t>27786; 49091</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15002; 34168</t>
+          <t>14552; 34194</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16534; 29265</t>
+          <t>16279; 29326</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26042; 50879</t>
+          <t>27363; 51347</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64158; 100314</t>
+          <t>62307; 98194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31143; 57982</t>
+          <t>32132; 59672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22193; 82560</t>
+          <t>23835; 81613</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27365; 52087</t>
+          <t>29214; 53182</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41344; 73479</t>
+          <t>39519; 70815</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28407; 53891</t>
+          <t>28093; 53933</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48568; 78074</t>
+          <t>47634; 77481</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43892; 73833</t>
+          <t>42266; 72481</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65270; 101637</t>
+          <t>67438; 103569</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55480; 90041</t>
+          <t>56609; 89912</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43312; 119230</t>
+          <t>51319; 120947</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80121; 118040</t>
+          <t>79434; 116013</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117681; 163785</t>
+          <t>116151; 162637</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92195; 132723</t>
+          <t>91313; 133375</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>108655; 178270</t>
+          <t>103682; 177334</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9574; 25653</t>
+          <t>10321; 26609</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10637; 26217</t>
+          <t>10006; 26304</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17039; 36579</t>
+          <t>16778; 36743</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26936; 49241</t>
+          <t>25908; 49339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40291; 68186</t>
+          <t>40081; 67355</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94576; 133570</t>
+          <t>94967; 135625</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94042; 133665</t>
+          <t>92628; 131701</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91151; 147836</t>
+          <t>95441; 149448</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52675; 86195</t>
+          <t>54845; 86711</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109402; 153910</t>
+          <t>110585; 155573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>115999; 163286</t>
+          <t>116108; 162841</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>132700; 185939</t>
+          <t>130469; 189039</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3290; 14441</t>
+          <t>2882; 14924</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5995</t>
+          <t>0; 6340</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>954; 9181</t>
+          <t>952; 9717</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6167; 27472</t>
+          <t>6725; 28562</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>74170; 111553</t>
+          <t>70041; 109908</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>117037; 162148</t>
+          <t>115841; 159271</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>101030; 144577</t>
+          <t>103771; 146162</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>79591; 112735</t>
+          <t>80141; 111810</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79043; 117838</t>
+          <t>80638; 118225</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>118187; 162120</t>
+          <t>115340; 160304</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106959; 151134</t>
+          <t>106591; 150136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>91257; 127364</t>
+          <t>90295; 129723</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>83536; 122928</t>
+          <t>82149; 123034</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>117353; 168315</t>
+          <t>116039; 168701</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91575; 133619</t>
+          <t>89592; 132190</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145780; 224933</t>
+          <t>148802; 223314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>223911; 283791</t>
+          <t>224139; 287667</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>367185; 442653</t>
+          <t>370279; 443386</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>321787; 401676</t>
+          <t>325621; 401272</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>334593; 446955</t>
+          <t>331557; 449010</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>321391; 395583</t>
+          <t>323350; 397896</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>495732; 593642</t>
+          <t>502844; 598488</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>427812; 518275</t>
+          <t>429476; 517282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>510437; 654685</t>
+          <t>514345; 647704</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1423-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,97</t>
+          <t>1,18; 4,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,69</t>
+          <t>1,56; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,7</t>
+          <t>1,23; 4,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,93</t>
+          <t>2,83; 6,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,02</t>
+          <t>2,82; 7,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,56</t>
+          <t>2,85; 8,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,9</t>
+          <t>2,71; 7,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 10,15</t>
+          <t>6,42; 10,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,9</t>
+          <t>2,27; 4,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,25</t>
+          <t>2,32; 5,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,18</t>
+          <t>2,47; 5,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,65</t>
+          <t>4,83; 7,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,23</t>
+          <t>0,99; 4,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,82</t>
+          <t>1,71; 5,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,23</t>
+          <t>1,02; 4,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,31</t>
+          <t>4,05; 8,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,08</t>
+          <t>3,87; 8,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,84</t>
+          <t>3,35; 8,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,82</t>
+          <t>2,3; 6,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 13,14</t>
+          <t>7,5; 12,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,62</t>
+          <t>2,84; 5,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,99</t>
+          <t>2,93; 6,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,78</t>
+          <t>2,12; 4,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,58</t>
+          <t>6,22; 9,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,38</t>
+          <t>2,41; 5,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,06</t>
+          <t>4,89; 8,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,96</t>
+          <t>2,5; 5,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,62</t>
+          <t>5,05; 9,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,3</t>
+          <t>6,33; 16,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,68; 18,87</t>
+          <t>10,95; 19,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 20,58</t>
+          <t>8,81; 20,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 17,57</t>
+          <t>9,74; 17,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,23</t>
+          <t>3,9; 7,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,04</t>
+          <t>7,12; 11,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,67</t>
+          <t>4,62; 8,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,77</t>
+          <t>6,96; 11,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,29</t>
+          <t>2,27; 4,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,11</t>
+          <t>3,53; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,69</t>
+          <t>2,51; 4,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,49</t>
+          <t>4,76; 7,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,15</t>
+          <t>6,26; 10,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,54</t>
+          <t>8,78; 13,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,89</t>
+          <t>6,94; 10,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,37</t>
+          <t>9,92; 13,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,94</t>
+          <t>4,02; 6,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,45</t>
+          <t>6,03; 8,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,75</t>
+          <t>4,68; 6,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,81</t>
+          <t>7,36; 9,62</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,59</t>
+          <t>2,79; 7,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,15</t>
+          <t>1,98; 5,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,92</t>
+          <t>2,84; 5,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,39</t>
+          <t>4,84; 9,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 11,84</t>
+          <t>6,81; 11,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,84</t>
+          <t>12,49; 17,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 17,84</t>
+          <t>12,77; 17,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,34; 17,76</t>
+          <t>14,89; 18,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,43</t>
+          <t>5,9; 9,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,24</t>
+          <t>8,65; 12,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 11,98</t>
+          <t>8,61; 11,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 14,36</t>
+          <t>11,14; 14,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,0</t>
+          <t>0,98; 4,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,38</t>
+          <t>0,33; 3,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,88</t>
+          <t>3,23; 12,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,8</t>
+          <t>5,85; 8,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,44; 14,36</t>
+          <t>10,41; 14,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,59; 13,51</t>
+          <t>9,63; 13,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,53; 14,69</t>
+          <t>10,33; 14,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,64</t>
+          <t>5,11; 7,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,38; 11,65</t>
+          <t>8,54; 11,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 10,97</t>
+          <t>7,84; 11,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,95</t>
+          <t>9,23; 13,16</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,76</t>
+          <t>2,57; 3,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 4,93</t>
+          <t>3,43; 4,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,9</t>
+          <t>2,72; 3,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,61</t>
+          <t>5,27; 6,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,52</t>
+          <t>6,74; 8,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,44; 12,5</t>
+          <t>10,4; 12,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,36</t>
+          <t>9,19; 11,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,27; 12,55</t>
+          <t>11,39; 13,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,98</t>
+          <t>4,82; 5,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,59</t>
+          <t>7,19; 8,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,48</t>
+          <t>6,21; 7,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,31</t>
+          <t>8,62; 9,88</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57883</t>
+          <t>63382</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5678; 18791</t>
+          <t>5583; 19354</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6146; 20517</t>
+          <t>6829; 22348</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5795; 20168</t>
+          <t>5280; 19839</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14738; 35004</t>
+          <t>15569; 34091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9051; 24603</t>
+          <t>8638; 24384</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7708; 23787</t>
+          <t>8973; 25542</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9903; 27403</t>
+          <t>9388; 27195</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26419; 45402</t>
+          <t>31370; 52246</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18125; 38270</t>
+          <t>17722; 37395</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17542; 39465</t>
+          <t>17474; 39803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18196; 40243</t>
+          <t>19142; 41469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46205; 72919</t>
+          <t>50190; 78832</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>70440</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3489; 15537</t>
+          <t>3620; 15437</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7138; 24390</t>
+          <t>7161; 24819</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3697; 15952</t>
+          <t>3850; 16207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17633; 37579</t>
+          <t>19565; 40687</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14485; 33748</t>
+          <t>14384; 32599</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12067; 29878</t>
+          <t>11335; 29113</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9241; 25377</t>
+          <t>8557; 24922</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29412; 50280</t>
+          <t>31744; 54337</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21138; 41527</t>
+          <t>20948; 42940</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21192; 45324</t>
+          <t>22188; 47584</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15514; 35819</t>
+          <t>15885; 36915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50447; 79993</t>
+          <t>56354; 88683</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54419</t>
+          <t>58829</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12334; 29176</t>
+          <t>13045; 30017</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29839; 57032</t>
+          <t>30799; 56607</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12932; 31094</t>
+          <t>13066; 30605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11519; 57600</t>
+          <t>23799; 45976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10236; 27352</t>
+          <t>10622; 27654</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27786; 49091</t>
+          <t>28481; 51073</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14552; 34194</t>
+          <t>14635; 34419</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16279; 29326</t>
+          <t>18262; 33063</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27363; 51347</t>
+          <t>27718; 53003</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62307; 98194</t>
+          <t>63291; 99684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32132; 59672</t>
+          <t>31820; 58823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23835; 81613</t>
+          <t>45853; 73880</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61257</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>89550</t>
+          <t>100233</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>150807</t>
+          <t>168565</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29214; 53182</t>
+          <t>28123; 51099</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39519; 70815</t>
+          <t>40860; 73547</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28093; 53933</t>
+          <t>28806; 54889</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47634; 77481</t>
+          <t>53841; 86742</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42266; 72481</t>
+          <t>44738; 73934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67438; 103569</t>
+          <t>67154; 100903</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56609; 89912</t>
+          <t>57315; 87864</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51319; 120947</t>
+          <t>85434; 117054</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79434; 116013</t>
+          <t>78563; 117278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116151; 162637</t>
+          <t>116069; 162771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91313; 133375</t>
+          <t>92356; 134289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>103682; 177334</t>
+          <t>146756; 191829</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>38503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>126106</t>
+          <t>138615</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>162433</t>
+          <t>177118</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10321; 26609</t>
+          <t>9775; 25165</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10006; 26304</t>
+          <t>10123; 26428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16778; 36743</t>
+          <t>17652; 37101</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25908; 49339</t>
+          <t>27488; 52612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40081; 67355</t>
+          <t>38718; 67971</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94967; 135625</t>
+          <t>94936; 136093</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92628; 131701</t>
+          <t>94251; 131620</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95441; 149448</t>
+          <t>123701; 157346</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54845; 86711</t>
+          <t>54277; 85623</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110585; 155573</t>
+          <t>109980; 153456</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116108; 162841</t>
+          <t>116954; 160541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>130469; 189039</t>
+          <t>155759; 198144</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>94052</t>
+          <t>102985</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>107350</t>
+          <t>118174</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2882; 14924</t>
+          <t>2932; 14542</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6340</t>
+          <t>0; 6514</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>952; 9717</t>
+          <t>956; 9641</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6725; 28562</t>
+          <t>7652; 28591</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>70041; 109908</t>
+          <t>73077; 109605</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>115841; 159271</t>
+          <t>115469; 160355</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>103771; 146162</t>
+          <t>104163; 145683</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>80141; 111810</t>
+          <t>87198; 120394</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80638; 118225</t>
+          <t>78988; 118780</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>115340; 160304</t>
+          <t>117592; 160943</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106591; 150136</t>
+          <t>107299; 151044</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>90295; 129723</t>
+          <t>99872; 142373</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>192278</t>
+          <t>208479</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>405486</t>
+          <t>448030</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>597764</t>
+          <t>656509</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>82149; 123034</t>
+          <t>84011; 124907</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116039; 168701</t>
+          <t>117376; 169843</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89592; 132190</t>
+          <t>91934; 134336</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148802; 223314</t>
+          <t>181493; 240130</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>224139; 287667</t>
+          <t>227628; 286568</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>370279; 443386</t>
+          <t>368875; 447206</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>325621; 401272</t>
+          <t>324602; 396854</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>331557; 449010</t>
+          <t>414142; 484415</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>323350; 397896</t>
+          <t>320777; 394750</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>502844; 598488</t>
+          <t>500913; 593610</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>429476; 517282</t>
+          <t>429311; 517923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>514345; 647704</t>
+          <t>610150; 699055</t>
         </is>
       </c>
     </row>
